--- a/backend/financial-statements/financial-statements-Aligned.xlsx
+++ b/backend/financial-statements/financial-statements-Aligned.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="9690" windowHeight="11370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="E-Cooking" sheetId="1" state="visible" r:id="rId1"/>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31.54296875" customWidth="1" min="1" max="1"/>
@@ -2780,12 +2780,12 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" thickBot="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Intangibles</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current assets </t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2796,46 +2796,46 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0</v>
+        <v>425.1680443402781</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>794.9537620231764</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
+        <v>1187.638718506397</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0</v>
+        <v>1603.123480807576</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0</v>
+        <v>2057.695719541563</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>2640.854774285605</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0</v>
+        <v>3217.838350625011</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3788.531412021446</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>4348.37468426295</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0</v>
+        <v>4910.760484751318</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0</v>
+        <v>5464.889170026301</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0</v>
+        <v>6084.614003035912</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" thickBot="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Other fixed assets</t>
+          <t>Cash and equivalents</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2849,49 +2849,49 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0</v>
+        <v>402.458858866241</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0</v>
+        <v>769.7215410731767</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0</v>
+        <v>1159.149641901858</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0</v>
+        <v>1571.377548548498</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0</v>
+        <v>2022.692931627946</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>2602.595130717449</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0</v>
+        <v>3176.321851402316</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>3742.973844289918</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>4298.743525836282</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0</v>
+        <v>4857.05573562951</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0</v>
+        <v>5407.110830209353</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>0</v>
+        <v>6022.762072523823</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" thickBot="1">
-      <c r="A42" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current assets </t>
-        </is>
-      </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Trade receivables</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2902,46 +2902,46 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>425.1680443402781</v>
+        <v>22.70918547403716</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>794.9537620231764</v>
+        <v>25.2322209499997</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1187.638718506397</v>
+        <v>28.48907660453873</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1603.123480807576</v>
+        <v>31.74593225907777</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>2057.695719541563</v>
+        <v>35.0027879136168</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2640.854774285605</v>
+        <v>38.25964356815583</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3217.838350625011</v>
+        <v>41.51649922269486</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3788.531412021446</v>
+        <v>45.55756773152763</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4348.37468426295</v>
+        <v>49.63115842666807</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4910.760484751318</v>
+        <v>53.7047491218085</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>5464.889170026301</v>
+        <v>57.77833981694894</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>6084.614003035912</v>
+        <v>61.85193051208937</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" thickBot="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Cash and equivalents</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2955,49 +2955,49 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>402.458858866241</v>
+        <v>0</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>769.7215410731767</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1159.149641901858</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1571.377548548498</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>2022.692931627946</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2602.595130717449</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3176.321851402316</v>
+        <v>0</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3742.973844289918</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4298.743525836282</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4857.05573562951</v>
+        <v>0</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>5407.110830209353</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>6022.762072523823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" thickBot="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Other financial assets</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3008,49 +3008,49 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0</v>
+        <v>698.0884968779322</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0</v>
+        <v>1393.384490668721</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0</v>
+        <v>2097.831919725327</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>2811.468829100731</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0</v>
+        <v>3550.718992664775</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>4405.216492217148</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>5270.311821503519</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>6145.041453409605</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>6994.329920966478</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0</v>
+        <v>7831.715455327872</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0</v>
+        <v>8646.542867647964</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0</v>
+        <v>9406.277500528318</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" thickBot="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Trade receivables</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>Total Shareholders' Equity</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3061,46 +3061,46 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>22.70918547403716</v>
+        <v>448.1534141654367</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>25.2322209499997</v>
+        <v>740.0103644375754</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>28.48907660453873</v>
+        <v>1073.664248243361</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>31.74593225907777</v>
+        <v>1393.875989233342</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>35.0027879136168</v>
+        <v>1701.268448222994</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>38.25964356815583</v>
+        <v>1999.227965025767</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>41.51649922269486</v>
+        <v>2294.297707196432</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>45.55756773152763</v>
+        <v>2617.148999730551</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>49.63115842666807</v>
+        <v>2951.408539536126</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>53.7047491218085</v>
+        <v>3269.503005303456</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>57.77833981694894</v>
+        <v>3571.458851706609</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>61.85193051208937</v>
+        <v>3833.386142132773</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" thickBot="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>Share capital &amp; treasury shares</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3114,46 +3114,46 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0</v>
+        <v>277.2</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" thickBot="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Other current tax assets</t>
+          <t>Retained earnings</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3167,49 +3167,49 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0</v>
+        <v>170.9534141654367</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0</v>
+        <v>189.8899118999213</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0</v>
+        <v>198.0335195978172</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0</v>
+        <v>206.4827880144126</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0</v>
+        <v>215.7230999298394</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>229.0046919025551</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0</v>
+        <v>252.7359892648895</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>287.4755288520428</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>317.6984981479656</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0</v>
+        <v>346.3477685999277</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0</v>
+        <v>373.3038811300558</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0</v>
+        <v>374.5324445111113</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1" thickBot="1">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3220,46 +3220,46 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>698.0884968779322</v>
+        <v>0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1393.384490668721</v>
+        <v>272.9204525376541</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2097.831919725327</v>
+        <v>598.4307286455444</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2811.468829100731</v>
+        <v>910.1932012189297</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>3550.718992664775</v>
+        <v>1208.345348293155</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4405.216492217148</v>
+        <v>1493.023273123212</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5270.311821503519</v>
+        <v>1764.361717931543</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>6145.041453409605</v>
+        <v>2052.473470878508</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>6994.329920966478</v>
+        <v>2356.51004138816</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7831.715455327872</v>
+        <v>2645.955236703528</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>8646.542867647964</v>
+        <v>2920.954970576554</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>9406.277500528318</v>
+        <v>3181.653697621662</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1" thickBot="1">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>Total Shareholders' Equity</t>
+          <t>Long term liabilities</t>
         </is>
       </c>
       <c r="B49" s="30" t="inlineStr">
@@ -3273,46 +3273,46 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>277.2</v>
+        <v>241.359598112997</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>277.2</v>
+        <v>468.5708229158245</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>277.2</v>
+        <v>696.5555354706238</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>277.2</v>
+        <v>925.3060008998751</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>277.2</v>
+        <v>1171.814561674834</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>277.2</v>
+        <v>1532.073636842043</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>277.2</v>
+        <v>1901.223637200306</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>277.2</v>
+        <v>2269.36</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>277.2</v>
+        <v>2603.360599171697</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>277.2</v>
+        <v>2913.216792351677</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>277.2</v>
+        <v>3184.840023599857</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>277.2</v>
+        <v>3401.896661371342</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" thickBot="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Share capital &amp; treasury shares</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Grants liabilities</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3326,46 +3326,46 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>277.2</v>
+        <v>241.359598112997</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>277.2</v>
+        <v>468.5708229158245</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>277.2</v>
+        <v>696.5555354706238</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>277.2</v>
+        <v>925.3060008998751</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>277.2</v>
+        <v>1154.814561674834</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>277.2</v>
+        <v>1385.073636842043</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>277.2</v>
+        <v>1609.223637200306</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>277.2</v>
+        <v>1827.36</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>277.2</v>
+        <v>2046.360599171697</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>277.2</v>
+        <v>2266.216792351677</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>277.2</v>
+        <v>2486.920023599857</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>277.2</v>
+        <v>2733.056661371342</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" thickBot="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Share premium</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>LT financial liabilities</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3391,37 +3391,37 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0</v>
+        <v>697.92</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>0</v>
+        <v>668.8399999999999</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" thickBot="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Short term liabilities</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3432,46 +3432,46 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>170.9534141654367</v>
+        <v>0</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>189.8899118999213</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>198.0335195978172</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>206.4827880144126</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>215.7230999298394</v>
+        <v>0</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>229.0046919025551</v>
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>252.7359892648895</v>
+        <v>0</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>287.4755288520428</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>317.6984981479656</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>346.3477685999277</v>
+        <v>0</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>373.3038811300558</v>
+        <v>0</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>374.5324445111113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" thickBot="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Reserves</t>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3488,46 +3488,46 @@
         <v>0</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>272.9204525376541</v>
+        <v>0</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>598.4307286455444</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>910.1932012189297</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1208.345348293155</v>
+        <v>0</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1493.023273123212</v>
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1764.361717931543</v>
+        <v>0</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2052.473470878508</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2356.51004138816</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2645.955236703528</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2920.954970576554</v>
+        <v>0</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3181.653697621662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" thickBot="1">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>Long term liabilities</t>
-        </is>
-      </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3538,152 +3538,154 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>241.359598112997</v>
+        <v>689.5130122784337</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>468.5708229158245</v>
+        <v>1208.5811873534</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>696.5555354706238</v>
+        <v>1770.219783713985</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>925.3060008998751</v>
+        <v>2319.181990133217</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1171.814561674834</v>
+        <v>2873.083009897829</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1532.073636842043</v>
+        <v>3531.30160186781</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1901.223637200306</v>
+        <v>4195.521344396739</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2269.36</v>
+        <v>4886.50899973055</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2603.360599171697</v>
+        <v>5554.769138707823</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2913.216792351677</v>
+        <v>6182.719797655132</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>3184.840023599857</v>
+        <v>6756.298875306466</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>3401.896661371342</v>
+        <v>7235.282803504115</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" thickBot="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Deferred tax liabilities</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0</v>
+        <v>8.575484599498509</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0</v>
+        <v>184.803303315321</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>327.6121360113416</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>492.2868389675132</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0</v>
+        <v>677.6359827669467</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>873.9148903493378</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0</v>
+        <v>1074.790477106781</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1258.532453679055</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1439.560782258655</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0</v>
+        <v>1648.99565767274</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0</v>
+        <v>1890.243992341498</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1" thickBot="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Grants liabilities</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>241.359598112997</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>468.5708229158245</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>696.5555354706238</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>925.3060008998751</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>1154.814561674834</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>1385.073636842043</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>1609.223637200306</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>1827.36</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>2046.360599171697</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>2266.216792351677</v>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>2486.920023599857</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>2733.056661371342</v>
+        <v>2170.994697024204</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" thickBot="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>CFS</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F56" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J56" s="21" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K56" s="21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L56" s="21" t="n">
+        <v>2031</v>
+      </c>
+      <c r="M56" s="21" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N56" s="21" t="n">
+        <v>2033</v>
+      </c>
+      <c r="O56" s="21" t="n">
+        <v>2034</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" thickBot="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>LT financial liabilities</t>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>- EBITDA (ex-Grants)</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3697,49 +3699,49 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0</v>
+        <v>158.1452728101806</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>175.2032632820317</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>197.8918575572139</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>220.8912003280865</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>17</v>
+        <v>244.1965721476355</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>147</v>
+        <v>267.8033168829379</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>292</v>
+        <v>291.706840920824</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>442</v>
+        <v>330.6556846741591</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>557</v>
+        <v>373.9755992394432</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>647</v>
+        <v>417.3903852826837</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>697.92</v>
+        <v>460.898521774777</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>668.8399999999999</v>
+        <v>504.4985086200535</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1" thickBot="1">
-      <c r="A58" s="29" t="inlineStr">
-        <is>
-          <t>Short term liabilities</t>
-        </is>
-      </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>- Taxes</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3750,46 +3752,46 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0</v>
+        <v>-41.90394921939088</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>-43.76599760662456</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>-47.23375694823976</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0</v>
+        <v>-50.81737633920262</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0</v>
+        <v>-54.70564582964373</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>-60.16257608268608</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0</v>
+        <v>-67.01566263122599</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>-78.18684675345327</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>-90.2763156243133</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0</v>
+        <v>-101.7504295810754</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0</v>
+        <v>-112.5627659248696</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0</v>
+        <v>-122.9313097765653</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" thickBot="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Trade payables</t>
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>- (+/-) Change in WC</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3803,49 +3805,49 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
+        <v>-14.13370087453862</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>-1.52817838792288</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0</v>
+        <v>-2.027658750550144</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0</v>
+        <v>-2.053199722798666</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0</v>
+        <v>-2.078352795292631</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>-2.103123171929887</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0</v>
+        <v>-2.127515991320323</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>-3.403328254482886</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>-3.764220457931053</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0</v>
+        <v>-3.772018113653509</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0</v>
+        <v>-3.77969075328523</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0</v>
+        <v>-3.787240097382487</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1" thickBot="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Other short term liabilities</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3856,46 +3858,46 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0</v>
+        <v>102.1076227162511</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0</v>
+        <v>129.9090872874843</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0</v>
+        <v>148.630441858424</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0</v>
+        <v>168.0206242660852</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0</v>
+        <v>187.4125735226992</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>205.5376176283219</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0</v>
+        <v>222.5636622982777</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>249.065509666223</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>279.9350631571989</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0</v>
+        <v>311.8679375879548</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0</v>
+        <v>344.5560650966221</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0</v>
+        <v>377.7799587461056</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" thickBot="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Other tax liabilities</t>
+          <t>Capex for e-cooking + electrification plan</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3909,49 +3911,49 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0</v>
+        <v>-281.4087638500101</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0</v>
+        <v>-344.4064050805485</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0</v>
+        <v>-340.962341029743</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0</v>
+        <v>-337.5527176194456</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0</v>
+        <v>-334.1771904432512</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>-330.8354185388187</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0</v>
+        <v>-358.0369416134102</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>-384.8135167786209</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>-380.9653816108346</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0</v>
+        <v>-377.1557277947263</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0</v>
+        <v>-373.384170516779</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>0</v>
+        <v>-260.1383164316352</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1" thickBot="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>ST financial liabilities</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>Investing Cash Flow</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3962,49 +3964,49 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0</v>
+        <v>-281.4087638500101</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0</v>
+        <v>-344.4064050805485</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0</v>
+        <v>-340.962341029743</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0</v>
+        <v>-337.5527176194456</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0</v>
+        <v>-334.1771904432512</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>-330.8354185388187</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0</v>
+        <v>-358.0369416134102</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>-384.8135167786209</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>-380.9653816108346</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0</v>
+        <v>-377.1557277947263</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0</v>
+        <v>-373.384170516779</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>0</v>
+        <v>-260.1383164316352</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" thickBot="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Provisions</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Cash Flow from Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4015,49 +4017,49 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0</v>
+        <v>-179.301141133759</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0</v>
+        <v>-214.4973177930642</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0</v>
+        <v>-192.331899171319</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0</v>
+        <v>-169.5320933533604</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0</v>
+        <v>-146.764616920552</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>-125.2978009104968</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0</v>
+        <v>-135.4732793151325</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>-135.7480071123979</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>-101.0303184536357</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0</v>
+        <v>-65.28779020677149</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0</v>
+        <v>-28.82810542015687</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>0</v>
+        <v>117.6416423144705</v>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1" thickBot="1">
-      <c r="A64" s="23" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Financial Expense</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4068,154 +4070,152 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>518.559598112997</v>
+        <v>0</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>745.7708229158245</v>
+        <v>0</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>973.7555354706237</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1202.506000899875</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1449.014561674834</v>
+        <v>-0.68</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1809.273636842043</v>
+        <v>-6.56</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2178.423637200306</v>
+        <v>-17.56</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2546.559999999999</v>
+        <v>-29.36</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2880.560599171697</v>
+        <v>-39.96</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3190.416792351677</v>
+        <v>-48.16</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3462.040023599857</v>
+        <v>-53.7968</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3679.096661371342</v>
+        <v>-54.67039999999999</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" thickBot="1">
-      <c r="A65" s="25" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B65" s="25" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Debt repayment</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>179.5288987649352</v>
+        <v>0</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>647.6136677528964</v>
+        <v>0</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>1124.076384254703</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1608.962828200855</v>
+        <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2101.704430989941</v>
+        <v>0</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2595.942855375105</v>
+        <v>0</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3091.888184303213</v>
+        <v>0</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3598.481453409606</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4113.769321794782</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4641.298662976195</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5184.502844048107</v>
+        <v>-29.08</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>5727.180839156977</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>CFS</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C66" s="20" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D66" s="21" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="E66" s="21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F66" s="21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G66" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H66" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I66" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J66" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K66" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="L66" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="M66" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="N66" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="O66" s="21" t="n">
-        <v>2034</v>
+        <v>-29.08</v>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1" thickBot="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Debt increase</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1" thickBot="1">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>- EBITDA (ex-Grants)</t>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Grants/Sub-debt financing</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -4229,46 +4229,46 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>158.1452728101806</v>
+        <v>304.56</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>175.2032632820317</v>
+        <v>304.56</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>197.8918575572139</v>
+        <v>304.56</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>220.8912003280865</v>
+        <v>304.56</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>244.1965721476355</v>
+        <v>304.56</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>267.8033168829379</v>
+        <v>304.56</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>291.706840920824</v>
+        <v>304.56</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>330.6556846741591</v>
+        <v>304.56</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>373.9755992394432</v>
+        <v>304.56</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>417.3903852826837</v>
+        <v>304.56</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>460.898521774777</v>
+        <v>304.56</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>504.4985086200535</v>
+        <v>304.56</v>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1" thickBot="1">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>- Taxes</t>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Dividends</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -4282,46 +4282,46 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>-41.90394921939088</v>
+        <v>0</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>-43.76599760662456</v>
+        <v>0</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-47.23375694823976</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-50.81737633920262</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>-54.70564582964373</v>
+        <v>0</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-60.16257608268608</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>-67.01566263122599</v>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-78.18684675345327</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>-90.2763156243133</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-101.7504295810754</v>
+        <v>0</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-112.5627659248696</v>
+        <v>0</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>-122.9313097765653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" thickBot="1">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>- (+/-) Change in WC</t>
+          <t>+/- Capital increase/reduction</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -4335,46 +4335,46 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>-14.13370087453862</v>
+        <v>0</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>-1.52817838792288</v>
+        <v>0</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-2.027658750550144</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-2.053199722798666</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>-2.078352795292631</v>
+        <v>0</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-2.103123171929887</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-2.127515991320323</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-3.403328254482886</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>-3.764220457931053</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-3.772018113653509</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-3.77969075328523</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>-3.787240097382487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1" thickBot="1">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Financing Cash Flow</t>
         </is>
       </c>
       <c r="B70" s="30" t="inlineStr">
@@ -4388,49 +4388,49 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>102.1076227162511</v>
+        <v>581.76</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>129.9090872874843</v>
+        <v>581.76</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>148.630441858424</v>
+        <v>581.76</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>168.0206242660852</v>
+        <v>581.76</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>187.4125735226992</v>
+        <v>598.0799999999999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>205.5376176283219</v>
+        <v>705.2</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>222.5636622982777</v>
+        <v>709.2</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>249.065509666223</v>
+        <v>702.4</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>279.9350631571989</v>
+        <v>656.8</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>311.8679375879548</v>
+        <v>623.5999999999999</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>344.5560650966221</v>
+        <v>578.8832</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>377.7799587461056</v>
+        <v>498.0096</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1" thickBot="1">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Capex for e-cooking + electrification plan</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>Cash movement</t>
+        </is>
+      </c>
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4441,49 +4441,49 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>-281.4087638500101</v>
+        <v>402.458858866241</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-344.4064050805485</v>
+        <v>367.2626822069358</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-340.962341029743</v>
+        <v>389.428100828681</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-337.5527176194456</v>
+        <v>412.2279066466396</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>-334.1771904432512</v>
+        <v>451.3153830794479</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-330.8354185388187</v>
+        <v>579.9021990895033</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>-358.0369416134102</v>
+        <v>573.7267206848676</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-384.8135167786209</v>
+        <v>566.6519928876021</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>-380.9653816108346</v>
+        <v>555.7696815463643</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-377.1557277947263</v>
+        <v>558.3122097932285</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-373.384170516779</v>
+        <v>550.0550945798432</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>-260.1383164316352</v>
+        <v>615.6512423144704</v>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1" thickBot="1">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>Investing Cash Flow</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Cash BoP</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4494,49 +4494,49 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>-281.4087638500101</v>
+        <v>0</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>-344.4064050805485</v>
+        <v>402.458858866241</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-340.962341029743</v>
+        <v>769.7215410731767</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-337.5527176194456</v>
+        <v>1159.149641901858</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>-334.1771904432512</v>
+        <v>1571.377548548498</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-330.8354185388187</v>
+        <v>2022.692931627946</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-358.0369416134102</v>
+        <v>2602.595130717449</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-384.8135167786209</v>
+        <v>3176.321851402316</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>-380.9653816108346</v>
+        <v>3742.973844289918</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-377.1557277947263</v>
+        <v>4298.743525836282</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-373.384170516779</v>
+        <v>4857.05573562951</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>-260.1383164316352</v>
+        <v>5407.110830209353</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" thickBot="1">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>Cash Flow from Assets</t>
-        </is>
-      </c>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>- Cash movement</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4547,46 +4547,46 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>-179.301141133759</v>
+        <v>402.458858866241</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>-214.4973177930642</v>
+        <v>367.2626822069358</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-192.331899171319</v>
+        <v>389.428100828681</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-169.5320933533604</v>
+        <v>412.2279066466396</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>-146.764616920552</v>
+        <v>451.3153830794479</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-125.2978009104968</v>
+        <v>579.9021990895033</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>-135.4732793151325</v>
+        <v>573.7267206848676</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-135.7480071123979</v>
+        <v>566.6519928876021</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>-101.0303184536357</v>
+        <v>555.7696815463643</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-65.28779020677149</v>
+        <v>558.3122097932285</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-28.82810542015687</v>
+        <v>550.0550945798432</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>117.6416423144705</v>
+        <v>615.6512423144704</v>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1" thickBot="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Financial Expense</t>
+          <t>Cash EoP</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4600,99 +4600,101 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0</v>
+        <v>402.458858866241</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0</v>
+        <v>769.7215410731767</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0</v>
+        <v>1159.149641901858</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0</v>
+        <v>1571.377548548498</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>-0.68</v>
+        <v>2022.692931627946</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-6.56</v>
+        <v>2602.595130717449</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-17.56</v>
+        <v>3176.321851402316</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-29.36</v>
+        <v>3742.973844289918</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>-39.96</v>
+        <v>4298.743525836282</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-48.16</v>
+        <v>4857.05573562951</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-53.7968</v>
+        <v>5407.110830209353</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>-54.67039999999999</v>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1" thickBot="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Debt repayment</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="2" t="n">
-        <v>-29.08</v>
-      </c>
-      <c r="O75" s="2" t="n">
-        <v>-29.08</v>
+        <v>6022.762072523823</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" thickBot="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>PP&amp;E - Capex</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E75" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F75" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G75" s="21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H75" s="21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I75" s="21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J75" s="21" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K75" s="21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L75" s="21" t="n">
+        <v>2031</v>
+      </c>
+      <c r="M75" s="21" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N75" s="21" t="n">
+        <v>2033</v>
+      </c>
+      <c r="O75" s="21" t="n">
+        <v>2034</v>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1" thickBot="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Debt increase</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4706,99 +4708,99 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0</v>
+        <v>281.4087638500101</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0</v>
+        <v>344.4064050805485</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0</v>
+        <v>340.962341029743</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0</v>
+        <v>337.5527176194456</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>17</v>
+        <v>334.1771904432512</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>130</v>
+        <v>330.8354185388187</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>145</v>
+        <v>358.0369416134102</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>150</v>
+        <v>384.8135167786209</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>115</v>
+        <v>380.9653816108346</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>90</v>
+        <v>377.1557277947263</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>80</v>
+        <v>373.384170516779</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>0</v>
+        <v>260.1383164316352</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1" thickBot="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Grants/Sub-debt financing</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>% Revenues</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>304.56</v>
+        <v>82.89028002713</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>304.56</v>
+        <v>89.60964019118744</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>304.56</v>
+        <v>80.56911045700559</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>304.56</v>
+        <v>73.05518192647203</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>304.56</v>
+        <v>66.71286092217544</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>304.56</v>
+        <v>61.28928354111073</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>304.56</v>
+        <v>61.14776822127532</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>304.56</v>
+        <v>60.0607281938192</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>304.56</v>
+        <v>55.26001294784286</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>304.56</v>
+        <v>51.09738609006735</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>304.56</v>
+        <v>47.45444356106954</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>304.56</v>
+        <v>32.07801389493282</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1" thickBot="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Dividends</t>
+          <t>PP&amp;E - BoP</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4815,43 +4817,43 @@
         <v>0</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0</v>
+        <v>272.9204525376541</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0</v>
+        <v>598.4307286455444</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0</v>
+        <v>910.1932012189297</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0</v>
+        <v>1208.345348293155</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>1493.023273123212</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0</v>
+        <v>1764.361717931543</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2052.473470878508</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2356.51004138816</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0</v>
+        <v>2645.955236703528</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0</v>
+        <v>2920.954970576554</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>0</v>
+        <v>3181.653697621662</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1" thickBot="1">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>+/- Capital increase/reduction</t>
+          <t>+ Capex</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4865,49 +4867,49 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0</v>
+        <v>281.4087638500101</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0</v>
+        <v>344.4064050805485</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0</v>
+        <v>340.962341029743</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0</v>
+        <v>337.5527176194456</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0</v>
+        <v>334.1771904432512</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>330.8354185388187</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0</v>
+        <v>358.0369416134102</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>384.8135167786209</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>380.9653816108346</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0</v>
+        <v>377.1557277947263</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0</v>
+        <v>373.384170516779</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>0</v>
+        <v>260.1383164316352</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1" thickBot="1">
-      <c r="A80" s="29" t="inlineStr">
-        <is>
-          <t>Financing Cash Flow</t>
-        </is>
-      </c>
-      <c r="B80" s="30" t="inlineStr">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>- Divestiture</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4918,49 +4920,49 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>581.76</v>
+        <v>0</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>581.76</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>581.76</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>581.76</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>598.0799999999999</v>
+        <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>705.2</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>709.2</v>
+        <v>0</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>702.4</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>656.8</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>623.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>578.8832</v>
+        <v>0</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>498.0096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" thickBot="1">
-      <c r="A81" s="29" t="inlineStr">
-        <is>
-          <t>Cash movement</t>
-        </is>
-      </c>
-      <c r="B81" s="30" t="inlineStr">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>- D&amp;A</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4971,46 +4973,46 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>402.458858866241</v>
+        <v>8.488311312355981</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>367.2626822069358</v>
+        <v>18.89612897265832</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>389.428100828681</v>
+        <v>29.19986845635764</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>412.2279066466396</v>
+        <v>39.40057054521996</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>451.3153830794479</v>
+        <v>49.49926561319366</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>579.9021990895033</v>
+        <v>59.49697373048763</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>573.7267206848676</v>
+        <v>69.92518866644555</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>566.6519928876021</v>
+        <v>80.77694626896894</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>555.7696815463643</v>
+        <v>91.52018629546711</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>558.3122097932285</v>
+        <v>102.1559939217003</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>550.0550945798432</v>
+        <v>112.6854434716712</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>615.6512423144704</v>
+        <v>120.1285165608916</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1" thickBot="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Cash BoP</t>
+          <t>PP&amp;E - EoP</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5024,99 +5026,101 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0</v>
+        <v>272.9204525376541</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>402.458858866241</v>
+        <v>598.4307286455444</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>769.7215410731767</v>
+        <v>910.1932012189297</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1159.149641901858</v>
+        <v>1208.345348293155</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1571.377548548498</v>
+        <v>1493.023273123212</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2022.692931627946</v>
+        <v>1764.361717931543</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2602.595130717449</v>
+        <v>2052.473470878508</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3176.321851402316</v>
+        <v>2356.51004138816</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3742.973844289918</v>
+        <v>2645.955236703528</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4298.743525836282</v>
+        <v>2920.954970576554</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>4857.05573562951</v>
+        <v>3181.653697621662</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>5407.110830209353</v>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1" thickBot="1">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>- Cash movement</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>402.458858866241</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>367.2626822069358</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>389.428100828681</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>412.2279066466396</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>451.3153830794479</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>579.9021990895033</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>573.7267206848676</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>566.6519928876021</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>555.7696815463643</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>558.3122097932285</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>550.0550945798432</v>
-      </c>
-      <c r="O83" s="2" t="n">
-        <v>615.6512423144704</v>
+        <v>3321.663497492406</v>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" thickBot="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>WCC</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F83" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G83" s="21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H83" s="21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I83" s="21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J83" s="21" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K83" s="21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L83" s="21" t="n">
+        <v>2031</v>
+      </c>
+      <c r="M83" s="21" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N83" s="21" t="n">
+        <v>2033</v>
+      </c>
+      <c r="O83" s="21" t="n">
+        <v>2034</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1" thickBot="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Cash EoP</t>
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>+ Trade receivables</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5130,101 +5134,99 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>402.458858866241</v>
+        <v>22.70918547403716</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>769.7215410731767</v>
+        <v>25.2322209499997</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1159.149641901858</v>
+        <v>28.48907660453873</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1571.377548548498</v>
+        <v>31.74593225907777</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>2022.692931627946</v>
+        <v>35.0027879136168</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2602.595130717449</v>
+        <v>38.25964356815583</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3176.321851402316</v>
+        <v>41.51649922269486</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3742.973844289918</v>
+        <v>45.55756773152763</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4298.743525836282</v>
+        <v>49.63115842666807</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4857.05573562951</v>
+        <v>53.7047491218085</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>5407.110830209353</v>
+        <v>57.77833981694894</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>6022.762072523823</v>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" thickBot="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>PP&amp;E - Capex</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="E85" s="21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F85" s="21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G85" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H85" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I85" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J85" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K85" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="L85" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="M85" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="N85" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="O85" s="21" t="n">
-        <v>2034</v>
+        <v>61.85193051208937</v>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1" thickBot="1">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>+ Inventories</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1" thickBot="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>- Trade payables</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5238,99 +5240,99 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>281.4087638500101</v>
+        <v>-8.575484599498541</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>344.4064050805485</v>
+        <v>-9.570341687538205</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>340.962341029743</v>
+        <v>-10.79953859152709</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>337.5527176194456</v>
+        <v>-12.00319452326746</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>334.1771904432512</v>
+        <v>-13.18169738251386</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>330.8354185388187</v>
+        <v>-14.33542986512301</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>358.0369416134102</v>
+        <v>-15.46476952834171</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>384.8135167786209</v>
+        <v>-16.1025097826916</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>380.9653816108346</v>
+        <v>-16.41188001990098</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>377.1557277947263</v>
+        <v>-16.71345260138791</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>373.384170516779</v>
+        <v>-17.00735254324311</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>260.1383164316352</v>
+        <v>-17.29370314100106</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1" thickBot="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>Working Capital</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>% Revenues</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>82.89028002713</v>
+        <v>14.13370087453862</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>89.60964019118744</v>
+        <v>15.6618792624615</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>80.56911045700559</v>
+        <v>17.68953801301164</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>73.05518192647203</v>
+        <v>19.74273773581031</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>66.71286092217544</v>
+        <v>21.82109053110294</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>61.28928354111073</v>
+        <v>23.92421370303283</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>61.14776822127532</v>
+        <v>26.05172969435315</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>60.0607281938192</v>
+        <v>29.45505794883604</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>55.26001294784286</v>
+        <v>33.21927840676709</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>51.09738609006735</v>
+        <v>36.9912965204206</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>47.45444356106954</v>
+        <v>40.77098727370583</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>32.07801389493282</v>
+        <v>44.55822737108831</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1" thickBot="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>PP&amp;E - BoP</t>
+          <t>Variation</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5344,99 +5346,123 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0</v>
+        <v>14.13370087453862</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>272.9204525376541</v>
+        <v>1.52817838792288</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>598.4307286455444</v>
+        <v>2.027658750550144</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>910.1932012189297</v>
+        <v>2.053199722798666</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>1208.345348293155</v>
+        <v>2.078352795292631</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1493.023273123212</v>
+        <v>2.103123171929887</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1764.361717931543</v>
+        <v>2.127515991320323</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2052.473470878508</v>
+        <v>3.403328254482886</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2356.51004138816</v>
+        <v>3.764220457931053</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2645.955236703528</v>
+        <v>3.772018113653509</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>2920.954970576554</v>
+        <v>3.77969075328523</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>3181.653697621662</v>
+        <v>3.787240097382487</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1" thickBot="1">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t>+ Capex</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>281.4087638500101</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>344.4064050805485</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>340.962341029743</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>337.5527176194456</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>334.1771904432512</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>330.8354185388187</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>358.0369416134102</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>384.8135167786209</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>380.9653816108346</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>377.1557277947263</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>373.384170516779</v>
-      </c>
-      <c r="O89" s="2" t="n">
-        <v>260.1383164316352</v>
+      <c r="A89" s="28" t="inlineStr">
+        <is>
+          <t>Working Capital Days</t>
+        </is>
+      </c>
+      <c r="B89" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1" thickBot="1">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>- Divestiture</t>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Trade receivables - Days of revenues</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5446,50 +5472,50 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1" thickBot="1">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>- D&amp;A</t>
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Inventories - Days of COGS</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5499,50 +5525,50 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>8.488311312355981</v>
+        <v>0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18.89612897265832</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>29.19986845635764</v>
+        <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>39.40057054521996</v>
+        <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.49926561319366</v>
+        <v>0</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>59.49697373048763</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>69.92518866644555</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>80.77694626896894</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>91.52018629546711</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>102.1559939217003</v>
+        <v>0</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>112.6854434716712</v>
+        <v>0</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>120.1285165608916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1" thickBot="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>PP&amp;E - EoP</t>
+          <t>Trade payables - Days of OPEX costs</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5552,50 +5578,50 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>272.9204525376541</v>
+        <v>30</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>598.4307286455444</v>
+        <v>30</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>910.1932012189297</v>
+        <v>30</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1208.345348293155</v>
+        <v>30</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>1493.023273123212</v>
+        <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1764.361717931543</v>
+        <v>30</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2052.473470878508</v>
+        <v>30</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2356.51004138816</v>
+        <v>30</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2645.955236703528</v>
+        <v>30</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2920.954970576554</v>
+        <v>30</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>3181.653697621662</v>
+        <v>30</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>3321.663497492406</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" thickBot="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -5648,12 +5674,12 @@
       </c>
     </row>
     <row r="94" ht="16" customHeight="1" thickBot="1">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>+ Trade receivables</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>Equity - BoP</t>
+        </is>
+      </c>
+      <c r="B94" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5664,46 +5690,46 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>22.70918547403716</v>
+        <v>0</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>25.2322209499997</v>
+        <v>448.1534141654367</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>28.48907660453873</v>
+        <v>915.243326065358</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>31.74593225907777</v>
+        <v>1390.476845663175</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.0027879136168</v>
+        <v>1874.159633677588</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>38.25964356815583</v>
+        <v>2367.082733607428</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>41.51649922269486</v>
+        <v>2873.287425509983</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>45.55756773152763</v>
+        <v>3403.223414774873</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>49.63115842666807</v>
+        <v>3967.898943626916</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>53.7047491218085</v>
+        <v>4562.797441774882</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>57.77833981694894</v>
+        <v>5186.34521037481</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>61.85193051208937</v>
+        <v>5836.849091504866</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1" thickBot="1">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>+ Inventories</t>
+          <t>+/- Capital Increase/Reduction</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5717,46 +5743,68 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O95" s="2" t="n">
-        <v>-0</v>
+        <v>277.2</v>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1" thickBot="1">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>- Trade payables</t>
+          <t>+/- Change in Equity/Net income</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5770,46 +5818,46 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>-8.575484599498541</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>-9.570341687538205</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>-10.79953859152709</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>-12.00319452326746</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>-13.18169738251386</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>-14.33542986512301</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>-15.46476952834171</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>-16.1025097826916</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>-16.41188001990098</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-16.71345260138791</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-17.00735254324311</v>
-      </c>
-      <c r="O96" s="2" t="n">
-        <v>-17.29370314100106</v>
+        <v>170.9534141654367</v>
+      </c>
+      <c r="E96" s="27" t="n">
+        <v>189.8899118999213</v>
+      </c>
+      <c r="F96" s="27" t="n">
+        <v>198.0335195978172</v>
+      </c>
+      <c r="G96" s="27" t="n">
+        <v>206.4827880144126</v>
+      </c>
+      <c r="H96" s="27" t="n">
+        <v>215.7230999298394</v>
+      </c>
+      <c r="I96" s="27" t="n">
+        <v>229.0046919025551</v>
+      </c>
+      <c r="J96" s="27" t="n">
+        <v>252.7359892648895</v>
+      </c>
+      <c r="K96" s="27" t="n">
+        <v>287.4755288520428</v>
+      </c>
+      <c r="L96" s="27" t="n">
+        <v>317.6984981479656</v>
+      </c>
+      <c r="M96" s="27" t="n">
+        <v>346.3477685999277</v>
+      </c>
+      <c r="N96" s="27" t="n">
+        <v>373.3038811300558</v>
+      </c>
+      <c r="O96" s="27" t="n">
+        <v>374.5324445111113</v>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1" thickBot="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Working Capital</t>
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>- Dividends (% Net Income)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5823,49 +5871,49 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>14.13370087453862</v>
+        <v>0</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15.6618792624615</v>
+        <v>0</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>17.68953801301164</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>19.74273773581031</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>21.82109053110294</v>
+        <v>0</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>23.92421370303283</v>
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>26.05172969435315</v>
+        <v>0</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>29.45505794883604</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>33.21927840676709</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>36.9912965204206</v>
+        <v>0</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>40.77098727370583</v>
+        <v>0</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>44.55822737108831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1" thickBot="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>Variation</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>Equity - EoP</t>
+        </is>
+      </c>
+      <c r="B98" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5876,395 +5924,371 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>14.13370087453862</v>
+        <v>448.1534141654367</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.52817838792288</v>
+        <v>915.243326065358</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>2.027658750550144</v>
+        <v>1390.476845663175</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>2.053199722798666</v>
+        <v>1874.159633677588</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>2.078352795292631</v>
+        <v>2367.082733607428</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2.103123171929887</v>
+        <v>2873.287425509983</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.127515991320323</v>
+        <v>3403.223414774873</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.403328254482886</v>
+        <v>3967.898943626916</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.764220457931053</v>
+        <v>4562.797441774882</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3.772018113653509</v>
+        <v>5186.34521037481</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>3.77969075328523</v>
+        <v>5836.849091504866</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>3.787240097382487</v>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1" thickBot="1">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>Working Capital Days</t>
-        </is>
-      </c>
-      <c r="B99" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6488.581536015977</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" thickBot="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F99" s="21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G99" s="21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H99" s="21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I99" s="21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J99" s="21" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K99" s="21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L99" s="21" t="n">
+        <v>2031</v>
+      </c>
+      <c r="M99" s="21" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N99" s="21" t="n">
+        <v>2033</v>
+      </c>
+      <c r="O99" s="21" t="n">
+        <v>2034</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1" thickBot="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Trade receivables - Days of revenues</t>
+          <t>GRANTS</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>% with grants</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" thickBot="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Inventories - Days of COGS</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>GRANTS</t>
+        </is>
+      </c>
+      <c r="B101" s="28" t="inlineStr">
+        <is>
+          <t>BoP</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0</v>
+        <v>241.359598112997</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>468.5708229158245</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
+        <v>696.5555354706238</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>0</v>
+        <v>925.3060008998751</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>1154.814561674834</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0</v>
+        <v>1385.073636842043</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1609.223637200306</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>1827.36</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0</v>
+        <v>2046.360599171697</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0</v>
+        <v>2266.216792351677</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>0</v>
+        <v>2486.920023599857</v>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" thickBot="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Trade payables - Days of OPEX costs</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>GRANTS</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>+ Increase</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>30</v>
+        <v>304.56</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" thickBot="1">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C103" s="20" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="E103" s="21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F103" s="21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G103" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H103" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I103" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J103" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K103" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="L103" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="M103" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="N103" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="O103" s="21" t="n">
-        <v>2034</v>
+        <v>304.56</v>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1" thickBot="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>GRANTS</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>- Realisation</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>-63.20040188700303</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>-77.34877519717247</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-76.57528744520074</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>-75.80953457074874</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>-75.05143922504126</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>-74.30092483279086</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>-80.40999964173699</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>-86.42363720030586</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>-85.5594008283028</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-84.70380682001976</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-83.8567687518196</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>-58.42336222851477</v>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1" thickBot="1">
-      <c r="A104" s="28" t="inlineStr">
-        <is>
-          <t>Equity - BoP</t>
-        </is>
-      </c>
-      <c r="B104" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>GRANTS</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>- Realisation (% capex)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0</v>
+        <v>10.37568982909821</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>448.1534141654367</v>
+        <v>12.69844615136139</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>915.243326065358</v>
+        <v>12.57146168984777</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1390.476845663175</v>
+        <v>12.44574707294929</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>1874.159633677588</v>
+        <v>12.3212896022198</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2367.082733607428</v>
+        <v>12.19807670619761</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2873.287425509983</v>
+        <v>13.20101123616644</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>3403.223414774873</v>
+        <v>14.18827771215949</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3967.898943626916</v>
+        <v>14.04639493503789</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4562.797441774882</v>
+        <v>13.90593098568751</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>5186.34521037481</v>
+        <v>13.76687167583064</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>5836.849091504866</v>
+        <v>9.591437192755905</v>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1" thickBot="1">
-      <c r="A105" s="12" t="inlineStr">
-        <is>
-          <t>+/- Capital Increase/Reduction</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>GRANTS</t>
+        </is>
+      </c>
+      <c r="B105" s="28" t="inlineStr">
+        <is>
+          <t>EoP</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -6273,73 +6297,51 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>277.2</v>
-      </c>
-      <c r="E105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>241.359598112997</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>468.5708229158245</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>696.5555354706238</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>925.3060008998751</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1154.814561674834</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1385.073636842043</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1609.223637200306</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1827.36</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>2046.360599171697</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>2266.216792351677</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>2486.920023599857</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>2733.056661371342</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" thickBot="1">
-      <c r="A106" s="12" t="inlineStr">
-        <is>
-          <t>+/- Change in Equity/Net income</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B106" s="28" t="inlineStr">
+        <is>
+          <t>BoP</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -6348,51 +6350,51 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>170.9534141654367</v>
-      </c>
-      <c r="E106" s="27" t="n">
-        <v>189.8899118999213</v>
-      </c>
-      <c r="F106" s="27" t="n">
-        <v>198.0335195978172</v>
-      </c>
-      <c r="G106" s="27" t="n">
-        <v>206.4827880144126</v>
-      </c>
-      <c r="H106" s="27" t="n">
-        <v>215.7230999298394</v>
-      </c>
-      <c r="I106" s="27" t="n">
-        <v>229.0046919025551</v>
-      </c>
-      <c r="J106" s="27" t="n">
-        <v>252.7359892648895</v>
-      </c>
-      <c r="K106" s="27" t="n">
-        <v>287.4755288520428</v>
-      </c>
-      <c r="L106" s="27" t="n">
-        <v>317.6984981479656</v>
-      </c>
-      <c r="M106" s="27" t="n">
-        <v>346.3477685999277</v>
-      </c>
-      <c r="N106" s="27" t="n">
-        <v>373.3038811300558</v>
-      </c>
-      <c r="O106" s="27" t="n">
-        <v>374.5324445111113</v>
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>647</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>697.92</v>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1" thickBot="1">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>- Dividends (% Net Income)</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>+ Increase</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -6413,39 +6415,39 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1" thickBot="1">
-      <c r="A108" s="28" t="inlineStr">
-        <is>
-          <t>Equity - EoP</t>
-        </is>
-      </c>
-      <c r="B108" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>- Repayment</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -6454,106 +6456,104 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>448.1534141654367</v>
+        <v>0</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>915.243326065358</v>
+        <v>0</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>1390.476845663175</v>
+        <v>0</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1874.159633677588</v>
+        <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>2367.082733607428</v>
+        <v>0</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2873.287425509983</v>
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>3403.223414774873</v>
+        <v>0</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>3967.898943626916</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4562.797441774882</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5186.34521037481</v>
+        <v>0</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>5836.849091504866</v>
+        <v>-29.08</v>
       </c>
       <c r="O108" s="2" t="n">
-        <v>6488.581536015977</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" thickBot="1">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C109" s="20" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="E109" s="21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F109" s="21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G109" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H109" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I109" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J109" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K109" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="L109" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="M109" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="N109" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="O109" s="21" t="n">
-        <v>2034</v>
+        <v>-29.08</v>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1" thickBot="1">
+      <c r="A109" s="28" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B109" s="28" t="inlineStr">
+        <is>
+          <t>EoP</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>647</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>697.92</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>668.8399999999999</v>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1" thickBot="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>GRANTS</t>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>% with grants</t>
+          <t>Interest rate LT</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -6562,51 +6562,73 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1" thickBot="1">
       <c r="A111" s="28" t="inlineStr">
         <is>
-          <t>GRANTS</t>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B111" s="28" t="inlineStr">
         <is>
-          <t>BoP</t>
+          <t>LT financial expense</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -6618,588 +6640,36 @@
         <v>0</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>241.359598112997</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>468.5708229158245</v>
+        <v>0</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>696.5555354706238</v>
+        <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>925.3060008998751</v>
+        <v>0.68</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1154.814561674834</v>
+        <v>6.56</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1385.073636842043</v>
+        <v>17.56</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1609.223637200306</v>
+        <v>29.36</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1827.36</v>
+        <v>39.96</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2046.360599171697</v>
+        <v>48.16</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>2266.216792351677</v>
+        <v>53.7968</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>2486.920023599857</v>
-      </c>
-    </row>
-    <row r="112" ht="16" customHeight="1" thickBot="1">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>GRANTS</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>+ Increase</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-      <c r="O112" s="2" t="n">
-        <v>304.56</v>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1" thickBot="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>GRANTS</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>- Realisation</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>-63.20040188700303</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>-77.34877519717247</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>-76.57528744520074</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>-75.80953457074874</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>-75.05143922504126</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>-74.30092483279086</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>-80.40999964173699</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>-86.42363720030586</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>-85.5594008283028</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-84.70380682001976</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>-83.8567687518196</v>
-      </c>
-      <c r="O113" s="2" t="n">
-        <v>-58.42336222851477</v>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1" thickBot="1">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>GRANTS</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t>- Realisation (% capex)</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>10.37568982909821</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>12.69844615136139</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>12.57146168984777</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>12.44574707294929</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>12.3212896022198</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>12.19807670619761</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>13.20101123616644</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>14.18827771215949</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>14.04639493503789</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>13.90593098568751</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>13.76687167583064</v>
-      </c>
-      <c r="O114" s="2" t="n">
-        <v>9.591437192755905</v>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1" thickBot="1">
-      <c r="A115" s="28" t="inlineStr">
-        <is>
-          <t>GRANTS</t>
-        </is>
-      </c>
-      <c r="B115" s="28" t="inlineStr">
-        <is>
-          <t>EoP</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>241.359598112997</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>468.5708229158245</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>696.5555354706238</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>925.3060008998751</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>1154.814561674834</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>1385.073636842043</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>1609.223637200306</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>1827.36</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>2046.360599171697</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>2266.216792351677</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>2486.920023599857</v>
-      </c>
-      <c r="O115" s="2" t="n">
-        <v>2733.056661371342</v>
-      </c>
-    </row>
-    <row r="116" ht="16" customHeight="1" thickBot="1">
-      <c r="A116" s="28" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
-      <c r="B116" s="28" t="inlineStr">
-        <is>
-          <t>BoP</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>442</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>557</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>647</v>
-      </c>
-      <c r="O116" s="2" t="n">
-        <v>697.92</v>
-      </c>
-    </row>
-    <row r="117" ht="16" customHeight="1" thickBot="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t>+ Increase</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="O117" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1" thickBot="1">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="inlineStr">
-        <is>
-          <t>- Repayment</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>-29.08</v>
-      </c>
-      <c r="O118" s="2" t="n">
-        <v>-29.08</v>
-      </c>
-    </row>
-    <row r="119" ht="16" customHeight="1" thickBot="1">
-      <c r="A119" s="28" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
-      <c r="B119" s="28" t="inlineStr">
-        <is>
-          <t>EoP</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>442</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>557</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>647</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>697.92</v>
-      </c>
-      <c r="O119" s="2" t="n">
-        <v>668.8399999999999</v>
-      </c>
-    </row>
-    <row r="120" ht="16" customHeight="1" thickBot="1">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>Interest rate LT</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O120" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1" thickBot="1">
-      <c r="A121" s="28" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
-      <c r="B121" s="28" t="inlineStr">
-        <is>
-          <t>LT financial expense</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>29.36</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>53.7968</v>
-      </c>
-      <c r="O121" s="2" t="n">
         <v>54.67039999999999</v>
       </c>
     </row>
@@ -9786,40 +9256,40 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>277.2</v>
+        <v>448.1534141654367</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>277.2</v>
+        <v>740.0103644375754</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>277.2</v>
+        <v>1073.664248243361</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>277.2</v>
+        <v>1393.875989233342</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>277.2</v>
+        <v>1701.268448222994</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>277.2</v>
+        <v>1999.227965025767</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>277.2</v>
+        <v>2294.297707196432</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>277.2</v>
+        <v>2617.148999730551</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>277.2</v>
+        <v>2951.408539536126</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>277.2</v>
+        <v>3269.503005303456</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>277.2</v>
+        <v>3571.458851706609</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>277.2</v>
+        <v>3833.386142132773</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" thickBot="1">
@@ -10581,40 +10051,40 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>518.559598112997</v>
+        <v>689.5130122784337</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>745.7708229158245</v>
+        <v>1208.5811873534</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>973.7555354706237</v>
+        <v>1770.219783713985</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1202.506000899875</v>
+        <v>2319.181990133217</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1449.014561674834</v>
+        <v>2873.083009897829</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1809.273636842043</v>
+        <v>3531.30160186781</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2178.423637200306</v>
+        <v>4195.521344396739</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2546.559999999999</v>
+        <v>4886.50899973055</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2880.560599171697</v>
+        <v>5554.769138707823</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3190.416792351677</v>
+        <v>6182.719797655132</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3462.040023599857</v>
+        <v>6756.298875306466</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3679.096661371342</v>
+        <v>7235.282803504115</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" thickBot="1">
@@ -10634,40 +10104,40 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>179.5288987649352</v>
+        <v>8.575484599498509</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>647.6136677528964</v>
+        <v>184.803303315321</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>1124.076384254703</v>
+        <v>327.6121360113416</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1608.962828200855</v>
+        <v>492.2868389675132</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2101.704430989941</v>
+        <v>677.6359827669467</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2595.942855375105</v>
+        <v>873.9148903493378</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3091.888184303213</v>
+        <v>1074.790477106781</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3598.481453409606</v>
+        <v>1258.532453679055</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4113.769321794782</v>
+        <v>1439.560782258655</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4641.298662976195</v>
+        <v>1648.99565767274</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5184.502844048107</v>
+        <v>1890.243992341498</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>5727.180839156977</v>
+        <v>2170.994697024204</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" thickBot="1">
@@ -16277,40 +15747,40 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>277.2</v>
+        <v>448.1534141654367</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>277.2</v>
+        <v>740.0103644375754</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>277.2</v>
+        <v>1073.664248243361</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>277.2</v>
+        <v>1393.875989233342</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>277.2</v>
+        <v>1701.268448222994</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>277.2</v>
+        <v>1999.227965025767</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>277.2</v>
+        <v>2294.297707196432</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>277.2</v>
+        <v>2617.148999730551</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>277.2</v>
+        <v>2951.408539536126</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>277.2</v>
+        <v>3269.503005303456</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>277.2</v>
+        <v>3571.458851706609</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>277.2</v>
+        <v>3833.386142132773</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" thickBot="1">
@@ -17072,40 +16542,40 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>518.559598112997</v>
+        <v>689.5130122784337</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>745.7708229158245</v>
+        <v>1208.5811873534</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>973.7555354706237</v>
+        <v>1770.219783713985</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1202.506000899875</v>
+        <v>2319.181990133217</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1449.014561674834</v>
+        <v>2873.083009897829</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1809.273636842043</v>
+        <v>3531.30160186781</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2178.423637200306</v>
+        <v>4195.521344396739</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2546.559999999999</v>
+        <v>4886.50899973055</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2880.560599171697</v>
+        <v>5554.769138707823</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3190.416792351677</v>
+        <v>6182.719797655132</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3462.040023599857</v>
+        <v>6756.298875306466</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3679.096661371342</v>
+        <v>7235.282803504115</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" thickBot="1">
@@ -17125,40 +16595,40 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>179.5288987649352</v>
+        <v>8.575484599498509</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>647.6136677528964</v>
+        <v>184.803303315321</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>1124.076384254703</v>
+        <v>327.6121360113416</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1608.962828200855</v>
+        <v>492.2868389675132</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2101.704430989941</v>
+        <v>677.6359827669467</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2595.942855375105</v>
+        <v>873.9148903493378</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3091.888184303213</v>
+        <v>1074.790477106781</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3598.481453409606</v>
+        <v>1258.532453679055</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4113.769321794782</v>
+        <v>1439.560782258655</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4641.298662976195</v>
+        <v>1648.99565767274</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5184.502844048107</v>
+        <v>1890.243992341498</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>5727.180839156977</v>
+        <v>2170.994697024204</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" thickBot="1">
@@ -23057,40 +22527,40 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>277.2</v>
+        <v>448.1534141654367</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>277.2</v>
+        <v>740.0103644375754</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>277.2</v>
+        <v>1073.664248243361</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>277.2</v>
+        <v>1393.875989233342</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>277.2</v>
+        <v>1701.268448222994</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>277.2</v>
+        <v>1999.227965025767</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>277.2</v>
+        <v>2294.297707196432</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>277.2</v>
+        <v>2617.148999730551</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>277.2</v>
+        <v>2951.408539536126</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>277.2</v>
+        <v>3269.503005303456</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>277.2</v>
+        <v>3571.458851706609</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>277.2</v>
+        <v>3833.386142132773</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" thickBot="1">
@@ -23852,40 +23322,40 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>518.559598112997</v>
+        <v>689.5130122784337</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>745.7708229158245</v>
+        <v>1208.5811873534</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>973.7555354706237</v>
+        <v>1770.219783713985</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1202.506000899875</v>
+        <v>2319.181990133217</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1449.014561674834</v>
+        <v>2873.083009897829</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1809.273636842043</v>
+        <v>3531.30160186781</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2178.423637200306</v>
+        <v>4195.521344396739</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2546.559999999999</v>
+        <v>4886.50899973055</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2880.560599171697</v>
+        <v>5554.769138707823</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3190.416792351677</v>
+        <v>6182.719797655132</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3462.040023599857</v>
+        <v>6756.298875306466</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3679.096661371342</v>
+        <v>7235.282803504115</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" thickBot="1">
@@ -23905,40 +23375,40 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>179.5288987649352</v>
+        <v>8.575484599498509</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>647.6136677528964</v>
+        <v>184.803303315321</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>1124.076384254703</v>
+        <v>327.6121360113416</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1608.962828200855</v>
+        <v>492.2868389675132</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2101.704430989941</v>
+        <v>677.6359827669467</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2595.942855375105</v>
+        <v>873.9148903493378</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3091.888184303213</v>
+        <v>1074.790477106781</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3598.481453409606</v>
+        <v>1258.532453679055</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4113.769321794782</v>
+        <v>1439.560782258655</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4641.298662976195</v>
+        <v>1648.99565767274</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5184.502844048107</v>
+        <v>1890.243992341498</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>5727.180839156977</v>
+        <v>2170.994697024204</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" thickBot="1">
